--- a/RATES.xlsx
+++ b/RATES.xlsx
@@ -1309,8 +1309,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010017B410758E375740B58B1570DC378760" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9bbfa38b1927fef44e108d7be44e208d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="988de5a7-9197-4362-a728-67ea1cf4fd84" xmlns:ns3="0e4095c6-7236-4258-9845-29a0ecddd781" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fe22b22b04d5e8bc6dd161f930585771" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010017B410758E375740B58B1570DC378760" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1375c759d5cbf67854886a28a6210c8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="988de5a7-9197-4362-a728-67ea1cf4fd84" xmlns:ns3="0e4095c6-7236-4258-9845-29a0ecddd781" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b745824f897efd37f7eb49839f552ca3" ns2:_="" ns3:_="">
     <xsd:import namespace="988de5a7-9197-4362-a728-67ea1cf4fd84"/>
     <xsd:import namespace="0e4095c6-7236-4258-9845-29a0ecddd781"/>
     <xsd:element name="properties">
@@ -1524,22 +1524,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E50B0C9-35B5-4D1C-BD95-57D7CA4D16F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="988de5a7-9197-4362-a728-67ea1cf4fd84"/>
-    <ds:schemaRef ds:uri="0e4095c6-7236-4258-9845-29a0ecddd781"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B5F68A8-9DBD-479C-B214-D4CD7B09E97A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1548,4 +1533,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" removed="0"/>
+</clbl:labelList>
 </file>